--- a/artfynd/S 1716-2026 artfynd.xlsx
+++ b/artfynd/S 1716-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135750620</v>
       </c>
       <c r="B2" t="n">
-        <v>98139</v>
+        <v>98141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1716-2026 artfynd.xlsx
+++ b/artfynd/S 1716-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135750620</v>
       </c>
       <c r="B2" t="n">
-        <v>98141</v>
+        <v>98158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1716-2026 artfynd.xlsx
+++ b/artfynd/S 1716-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135750620</v>
       </c>
       <c r="B2" t="n">
-        <v>98158</v>
+        <v>98159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1716-2026 artfynd.xlsx
+++ b/artfynd/S 1716-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135750620</v>
       </c>
       <c r="B2" t="n">
-        <v>98159</v>
+        <v>98160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1716-2026 artfynd.xlsx
+++ b/artfynd/S 1716-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135750620</v>
       </c>
       <c r="B2" t="n">
-        <v>98160</v>
+        <v>98161</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1716-2026 artfynd.xlsx
+++ b/artfynd/S 1716-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135750620</v>
       </c>
       <c r="B2" t="n">
-        <v>98161</v>
+        <v>98167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1716-2026 artfynd.xlsx
+++ b/artfynd/S 1716-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135750620</v>
       </c>
       <c r="B2" t="n">
-        <v>98167</v>
+        <v>98168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1716-2026 artfynd.xlsx
+++ b/artfynd/S 1716-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135750620</v>
       </c>
       <c r="B2" t="n">
-        <v>98168</v>
+        <v>98179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1716-2026 artfynd.xlsx
+++ b/artfynd/S 1716-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135750620</v>
       </c>
       <c r="B2" t="n">
-        <v>98179</v>
+        <v>98192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
